--- a/sample-data-10mins.xlsx
+++ b/sample-data-10mins.xlsx
@@ -8,36 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rasool Khan\OneDrive - University of Stirling\Desktop\DataTeach\Power BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986194BF-C3D5-49CD-AC57-28870BC38C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24438C1-C9AF-4327-98F6-538FA8629150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{B5EDF9BD-1E30-49E2-8BAB-62D2F4385782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{B5EDF9BD-1E30-49E2-8BAB-62D2F4385782}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet7" sheetId="8" r:id="rId8"/>
     <sheet name="Sheet8" sheetId="9" r:id="rId9"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet4!$J$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet4!$J$2</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet4!$J$3</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet4!$J$4</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet4!$J$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet4!$K$1:$O$1</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet4!$K$2:$O$2</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet4!$K$3:$O$3</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet4!$K$4:$O$4</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet4!$K$5:$O$5</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -59,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="128">
   <si>
     <t>Jehu Rudeforth</t>
   </si>
@@ -429,6 +417,21 @@
   <si>
     <t>Apr</t>
   </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Worth</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
 </sst>
 </file>
 
@@ -623,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -638,32 +641,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -681,12 +680,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -777,16 +770,40 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color theme="0" tint="-0.24994659260841701"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
+          <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2824,6 +2841,496 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.40949300087489071"/>
+          <c:y val="3.2407407407407406E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet7!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Years</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet7!$K$2:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3BC1-4969-8337-AB6404206B07}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet7!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Worth</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet7!$L$2:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>325000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>415000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>469000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>569000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3BC1-4969-8337-AB6404206B07}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="996508272"/>
+        <c:axId val="996510192"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="996508272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="996510192"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="996510192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="996508272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3113,6 +3620,307 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="362042559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet8!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Balance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet8!$K$2:$K$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>August</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet8!$L$2:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9CBC-48D2-80C2-471EFB9A0D6F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1499595392"/>
+        <c:axId val="1499608352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1499595392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1499608352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1499608352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1499595392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4716,6 +5524,764 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.33280555555555558"/>
+          <c:y val="5.0925925925925923E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attendence %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="accent1"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="lt1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4">
+                  <a:alpha val="70000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                          <a:lumOff val="40000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Amar</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Annie</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Lucy</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sharon</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Krithi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C746-4B60-A95E-A9E8BD1D3C6B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="269"/>
+        <c:overlap val="-20"/>
+        <c:axId val="362021919"/>
+        <c:axId val="362015199"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="362021919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t> Students</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362015199"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="362015199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>marks</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362021919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attendence %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$J$2:$J$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$K$2:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC3D-4D65-9607-2D3365CD1E78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="362505631"/>
+        <c:axId val="362506111"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="362505631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362506111"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="362506111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362505631"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5063,7 +6629,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5621,764 +7187,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.33280555555555558"/>
-          <c:y val="5.0925925925925923E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet5!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Attendence %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:pattFill prst="ltUpDiag">
-              <a:fgClr>
-                <a:schemeClr val="accent1"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:schemeClr val="lt1"/>
-              </a:bgClr>
-            </a:pattFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4472C4">
-                  <a:alpha val="70000"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent1">
-                          <a:lumMod val="60000"/>
-                          <a:lumOff val="40000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet5!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Amar</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Annie</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Lucy</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Sharon</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Krithi</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet5!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>91</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C746-4B60-A95E-A9E8BD1D3C6B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="269"/>
-        <c:overlap val="-20"/>
-        <c:axId val="362021919"/>
-        <c:axId val="362015199"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="362021919"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-IN"/>
-                  <a:t> Students</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="362015199"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="362015199"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>marks</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="362021919"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="accent1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="accent1"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet5!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Attendence %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet5!$J$2:$J$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>January</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>February</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>March</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>April</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>May</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet5!$K$2:$K$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>91</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DC3D-4D65-9607-2D3365CD1E78}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="362505631"/>
-        <c:axId val="362506111"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="362505631"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="362506111"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="362506111"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="362505631"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6892,6 +7700,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -8728,7 +9616,7 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8836,6 +9724,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -8846,6 +9739,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -8877,6 +9775,1028 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10746,7 +12666,543 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="214">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10854,6 +13310,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -10864,6 +13325,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -10895,6 +13361,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -11248,8 +13717,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11357,11 +13826,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -11372,11 +13836,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -11408,9 +13867,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -11760,542 +14216,6 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="214">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:styleClr val="auto"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltUpDiag">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltUpDiag">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
-          <a:schemeClr val="phClr"/>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="22225">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="35000"/>
-          <a:lumOff val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:glow rad="25400">
-          <a:schemeClr val="lt1"/>
-        </a:glow>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-            <a:tint val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -13478,6 +15398,83 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>102870</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>712470</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1371D9C-8D0F-F17B-2270-B44100EAFF4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>278130</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDE7D11-8780-72ED-C362-094D20A24CC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>213360</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
@@ -13530,83 +15527,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ECDE91B-B24B-7A37-0A26-C3C0A6F52D63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>102870</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>712470</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1371D9C-8D0F-F17B-2270-B44100EAFF4A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>278130</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDE7D11-8780-72ED-C362-094D20A24CC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13742,6 +15662,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>560070</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>377190</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5C46225-CB31-F349-C02D-19F9BBF76287}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13749,16 +15705,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>384810</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>201930</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13778,6 +15734,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{050DDF31-61AA-1D7D-E001-3C356C3D7109}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -13977,7 +15969,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{298B9A2B-79A8-4D18-AE65-4C21EB666CC6}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{298B9A2B-79A8-4D18-AE65-4C21EB666CC6}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -14055,7 +16047,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{33997672-B81B-4C62-9414-FD99F19309B7}" name="Table1" displayName="Table1" ref="A1:F1095" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{33997672-B81B-4C62-9414-FD99F19309B7}" name="Table1" displayName="Table1" ref="A1:F1095" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A1:F1095" xr:uid="{33997672-B81B-4C62-9414-FD99F19309B7}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{996558BD-4422-4408-9ABE-9FA92A55335E}" name="Sales Person" dataDxfId="6"/>
@@ -14070,6 +16062,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{42E2AF58-7FB2-4AEA-AC59-A8ED9F01D533}" name="Table2" displayName="Table2" ref="J1:K6" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="J1:K6" xr:uid="{42E2AF58-7FB2-4AEA-AC59-A8ED9F01D533}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{86A15B8E-8A93-4CCF-8D4C-D38CC6A61A6C}" name="Days"/>
+    <tableColumn id="2" xr3:uid="{3767CC05-37FD-4262-A382-9A40C81A2176}" name="Temp"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{857EC0C2-107D-4B6F-BFCD-D11D40D15614}" name="Table4" displayName="Table4" ref="J1:O5" totalsRowShown="0">
   <autoFilter ref="J1:O5" xr:uid="{857EC0C2-107D-4B6F-BFCD-D11D40D15614}"/>
   <tableColumns count="6">
@@ -36355,39 +38358,39 @@
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="5">
         <v>44774</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="7">
         <v>7896</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="20">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="23">
         <v>44749</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="24">
         <v>4501</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="25">
         <v>91</v>
       </c>
     </row>
@@ -36395,39 +38398,39 @@
       <c r="A5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="5">
         <v>44678</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="7">
         <v>12726</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="20">
         <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="23">
         <v>44616</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="24">
         <v>13685</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="25">
         <v>184</v>
       </c>
     </row>
@@ -36435,39 +38438,39 @@
       <c r="A7" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="4">
         <v>0</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="5">
         <v>44718</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="7">
         <v>5376</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="20">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="23">
         <v>44586</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="24">
         <v>13685</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="25">
         <v>176</v>
       </c>
     </row>
@@ -36475,39 +38478,39 @@
       <c r="A9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="5">
         <v>44644</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="7">
         <v>3080</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="20">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="23">
         <v>44671</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="24">
         <v>3990</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="25">
         <v>59</v>
       </c>
     </row>
@@ -36515,39 +38518,39 @@
       <c r="A11" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="5">
         <v>44746</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="7">
         <v>2835</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="20">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="23">
         <v>44574</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="24">
         <v>4704</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="25">
         <v>62</v>
       </c>
     </row>
@@ -36555,39 +38558,39 @@
       <c r="A13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="4">
         <v>0</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="5">
         <v>44630</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="7">
         <v>3703</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="20">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="23">
         <v>44574</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="24">
         <v>1442</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="25">
         <v>286</v>
       </c>
     </row>
@@ -36595,39 +38598,39 @@
       <c r="A15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="5">
         <v>44770</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="7">
         <v>168</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="20">
         <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="23">
         <v>44776</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="24">
         <v>8379</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="25">
         <v>173</v>
       </c>
     </row>
@@ -36635,39 +38638,39 @@
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="5">
         <v>44587</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="7">
         <v>6790</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="20">
         <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="23">
         <v>44606</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="24">
         <v>4067</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>42</v>
       </c>
     </row>
@@ -36774,7 +38777,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>60</v>
       </c>
       <c r="B3" t="s">
@@ -36785,86 +38788,84 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4">
         <v>6357.75</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4">
         <v>873</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5">
         <v>2754.5</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5">
         <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6">
         <v>9348.5</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6">
         <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7">
         <v>5924.333333333333</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7">
         <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8">
         <v>4179</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8">
         <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9">
         <v>3703</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11">
         <v>6020.411764705882</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11">
         <v>2425</v>
       </c>
     </row>
@@ -36888,10 +38889,10 @@
       <c r="B1" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="28" t="s">
         <v>103</v>
       </c>
     </row>
@@ -36957,6 +38958,104 @@
       </c>
       <c r="K6">
         <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E69C8E-1560-41CE-83AC-00A3A7DBAC5A}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2">
+        <v>77</v>
+      </c>
+      <c r="J2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>85</v>
+      </c>
+      <c r="J4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5">
+        <v>88</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6">
+        <v>91</v>
+      </c>
+      <c r="J6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -36965,7 +39064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8F2433-BE38-4B9C-A974-83AE1EAECF36}">
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -36975,10 +39074,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="28" t="s">
         <v>72</v>
       </c>
       <c r="J1" t="s">
@@ -37095,117 +39194,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E69C8E-1560-41CE-83AC-00A3A7DBAC5A}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2">
-        <v>77</v>
-      </c>
-      <c r="J2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3">
-        <v>69</v>
-      </c>
-      <c r="J3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4">
-        <v>85</v>
-      </c>
-      <c r="J4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K4">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5">
-        <v>88</v>
-      </c>
-      <c r="J5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6">
-        <v>91</v>
-      </c>
-      <c r="J6" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69C6AC4-CF75-414E-8169-CA565407F195}">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="28" t="s">
         <v>118</v>
       </c>
     </row>
@@ -37281,30 +39285,36 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1EB6F9-3D48-453F-8E14-16708166D236}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="28" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K1" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -37324,8 +39334,14 @@
         <f>AVERAGE(B2:E2)</f>
         <v>70.25</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K2">
+        <v>2021</v>
+      </c>
+      <c r="L2">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -37345,8 +39361,14 @@
         <f t="shared" ref="F3:F6" si="0">AVERAGE(B3:E3)</f>
         <v>85.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K3">
+        <v>2022</v>
+      </c>
+      <c r="L3">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -37366,8 +39388,14 @@
         <f t="shared" si="0"/>
         <v>70.75</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K4">
+        <v>2023</v>
+      </c>
+      <c r="L4">
+        <v>415000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -37387,8 +39415,14 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <v>2024</v>
+      </c>
+      <c r="L5">
+        <v>469000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -37407,6 +39441,12 @@
       <c r="F6">
         <f t="shared" si="0"/>
         <v>90.75</v>
+      </c>
+      <c r="K6">
+        <v>2025</v>
+      </c>
+      <c r="L6">
+        <v>569000</v>
       </c>
     </row>
   </sheetData>
@@ -37417,58 +39457,94 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53185C44-1F8C-4119-8CDB-78F3C933D0C2}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>96</v>
       </c>
       <c r="B1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K1" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>98</v>
       </c>
       <c r="B2">
         <v>134</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>99</v>
       </c>
       <c r="B3">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>83</v>
       </c>
       <c r="B4">
         <v>151</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>100</v>
       </c>
       <c r="B5">
         <v>168</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>101</v>
       </c>
       <c r="B6">
         <v>177</v>
+      </c>
+      <c r="K6" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6">
+        <v>7300</v>
       </c>
     </row>
   </sheetData>
